--- a/_Drive/Publicacoes/hugo.xlsx
+++ b/_Drive/Publicacoes/hugo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="hugo.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,41 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="5" count="5">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1080/00084433.2017.1409946</t>
+  </si>
+  <si>
+    <t>10.1016/S0921-5093(02)00604-4</t>
+  </si>
+  <si>
+    <t>10.1016/j.fusengdes.2017.11.003</t>
+  </si>
+  <si>
+    <t>10.1016/j.jmmm.2020.167702</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +92,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,847 +110,845 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A121"/>
+  <dimension ref="A1:A122"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="39.28335336538462" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1016/j.msea.2017.07.010</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.3139/147.110521</t>
+          <t>10.1016/j.msea.2017.07.010</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1016/j.scriptamat.2007.01.032</t>
+          <t>10.3139/147.110521</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.558-559.313</t>
+          <t>10.1016/j.scriptamat.2007.01.032</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.498-499.55</t>
+          <t>10.4028/www.scientific.net/MSF.558-559.313</t>
         </is>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/SSP.105.315</t>
+          <t>10.4028/www.scientific.net/MSF.498-499.55</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2013.09.008</t>
+          <t>10.4028/www.scientific.net/SSP.105.315</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392011005000014</t>
+          <t>10.1016/j.jnucmat.2013.09.008</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2011.06.012</t>
+          <t>10.1590/S1516-14392011005000014</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.416-418.251</t>
+          <t>10.1016/j.ijrmhm.2011.06.012</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2010.10.051</t>
+          <t>10.4028/www.scientific.net/MSF.416-418.251</t>
         </is>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10.1590/S0370-44672009000200007</t>
+          <t>10.1016/j.msea.2010.10.051</t>
         </is>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1007/s11661-014-2401-3</t>
+          <t>10.1590/S0370-44672009000200007</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1590/S0370-44672010000200012</t>
+          <t>10.1007/s11661-014-2401-3</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1155/2016/7093071</t>
+          <t>10.1590/S0370-44672010000200012</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2006.08.159</t>
+          <t>10.1155/2016/7093071</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1088/1757-899X/82/1/012060</t>
+          <t>10.1016/j.jallcom.2006.08.159</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.638-642.3009</t>
+          <t>10.1088/1757-899X/82/1/012060</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1016/j.addma.2019.100979</t>
+          <t>10.4028/www.scientific.net/MSF.638-642.3009</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2008.09.004</t>
+          <t>10.1016/j.addma.2019.100979</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2016.12.019</t>
+          <t>10.1016/j.jallcom.2008.09.004</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2011.11.051</t>
+          <t>10.1016/j.jnucmat.2016.12.019</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1016/S1359-6462(99)00331-0</t>
+          <t>10.1016/j.msea.2011.11.051</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2019.03.116</t>
+          <t>10.1016/S1359-6462(99)00331-0</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.667-669.373</t>
+          <t>10.1016/j.msea.2019.03.116</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1007/s10853-010-4462-z</t>
+          <t>10.4028/www.scientific.net/MSF.667-669.373</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1007/s10853-007-1515-z</t>
+          <t>10.1007/s10853-010-4462-z</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2005.864287</t>
+          <t>10.1007/s10853-007-1515-z</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2011.01.007</t>
+          <t>10.1109/TASC.2005.864287</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2008.920575</t>
+          <t>10.1016/j.msea.2011.01.007</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2012.12.017</t>
+          <t>10.1109/TASC.2008.920575</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1051/jp4:1996827</t>
+          <t>10.1016/j.jnucmat.2012.12.017</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.1080/00084433.2017.1409946</t>
+          <t>10.1051/jp4:1996827</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchar.2016.03.023</t>
-        </is>
+      <c r="A34" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2016.12.025</t>
+          <t>10.1016/j.matchar.2016.03.023</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/19/12/002</t>
+          <t>10.1016/j.jnucmat.2016.12.025</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.4322/tmm.2011.021</t>
+          <t>10.1088/0953-2048/19/12/002</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392005000300002</t>
+          <t>10.4322/tmm.2011.021</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/msf.753.333</t>
+          <t>10.1590/S1516-14392005000300002</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1016/S0921-5093(02)00604-4</t>
+          <t>10.4028/www.scientific.net/msf.753.333</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>10.1016/S0921-5093(03)00011-X</t>
-        </is>
+      <c r="A41" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1016/S1044-5803(00)00070-X</t>
+          <t>10.1016/S0921-5093(03)00011-X</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2020.07.038</t>
+          <t>10.1016/S1044-5803(00)00070-X</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2014.12.112</t>
+          <t>10.1016/j.actamat.2020.07.038</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2017.10.026</t>
+          <t>10.1016/j.jnucmat.2014.12.112</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.1016/j.fusengdes.2013.04.005</t>
+          <t>10.1016/j.actamat.2017.10.026</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10.1016/S1359-6462(01)01087-9</t>
+          <t>10.1016/j.fusengdes.2013.04.005</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1051/epjconf/20147504012</t>
+          <t>10.1016/S1359-6462(01)01087-9</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/16/3/301</t>
+          <t>10.1051/epjconf/20147504012</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2008.07.002</t>
+          <t>10.1088/0953-2048/16/3/301</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10.1590/1980-5373-mr-2017-0288</t>
+          <t>10.1016/j.msea.2008.07.002</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2006.05.110</t>
+          <t>10.1590/1980-5373-mr-2017-0288</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.1016/j.fusengdes.2017.11.003</t>
+          <t>10.1016/j.msea.2006.05.110</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>10.1016/j.jnucmat.2014.01.032</t>
-        </is>
+      <c r="A54" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1524/zksu.2009.0017</t>
+          <t>10.1016/j.jnucmat.2014.01.032</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2017.05.027</t>
+          <t>10.1524/zksu.2009.0017</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10.1016/S0921-5093(01)01323-5</t>
+          <t>10.1016/j.jnucmat.2017.05.027</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.1590/S1516-14392005000300012</t>
+          <t>10.1016/S0921-5093(01)01323-5</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.1023/A:1017584120460</t>
+          <t>10.1590/S1516-14392005000300012</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2010.02.051</t>
+          <t>10.1023/A:1017584120460</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.1016/j.scriptamat.2004.07.026</t>
+          <t>10.1016/j.msea.2010.02.051</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/KEM.189-191.296</t>
+          <t>10.1016/j.scriptamat.2004.07.026</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/18/1/006</t>
+          <t>10.4028/www.scientific.net/KEM.189-191.296</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.715-716.629</t>
+          <t>10.1088/0953-2048/18/1/006</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10.1016/j.jmmm.2020.167702</t>
+          <t>10.4028/www.scientific.net/MSF.715-716.629</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmmm.2018.10.034</t>
-        </is>
+      <c r="A66" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2015.10.110</t>
+          <t>10.1016/j.jmmm.2018.10.034</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10.1016/S0263-4368(02)00017-3</t>
+          <t>10.1016/j.msea.2015.10.110</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2019.04.014</t>
+          <t>10.1016/S0263-4368(02)00017-3</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10.1109/TASC.2004.830467</t>
+          <t>10.1016/j.msea.2019.04.014</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10.3390/molecules24010089</t>
+          <t>10.1109/TASC.2004.830467</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2015.03.020</t>
+          <t>10.3390/molecules24010089</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10.1016/S0263-4368(99)00035-9</t>
+          <t>10.1016/j.jnucmat.2015.03.020</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10.1088/1757-899x/97/1/012006</t>
+          <t>10.1016/S0263-4368(99)00035-9</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2005.11.041</t>
+          <t>10.1088/1757-899x/97/1/012006</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10.1016/j.jmmm.2016.06.027</t>
+          <t>10.1016/j.msea.2005.11.041</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10.1016/j.apsusc.2012.09.060</t>
+          <t>10.1016/j.jmmm.2016.06.027</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.467-470.513</t>
+          <t>10.1016/j.apsusc.2012.09.060</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10.1016/S0263-4368(00)00020-2</t>
+          <t>10.4028/www.scientific.net/MSF.467-470.513</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/18/9/001</t>
+          <t>10.1016/S0263-4368(00)00020-2</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2003.11.052</t>
+          <t>10.1088/0953-2048/18/9/001</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2004.09.032</t>
+          <t>10.1016/j.msea.2003.11.052</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.495-497.393</t>
+          <t>10.1016/j.msea.2004.09.032</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10.1016/S0010-938X(98)00187-5</t>
+          <t>10.4028/www.scientific.net/MSF.495-497.393</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.638-642.1995</t>
+          <t>10.1016/S0010-938X(98)00187-5</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10.1590/S0370-44672007000100018</t>
+          <t>10.4028/www.scientific.net/MSF.638-642.1995</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2007.02.086</t>
+          <t>10.1590/S0370-44672007000100018</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10.1016/S0263-4368(98)00027-4</t>
+          <t>10.1016/j.msea.2007.02.086</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10.1007/s10800-011-0320-1</t>
+          <t>10.1016/S0263-4368(98)00027-4</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/DDF.283-286.38</t>
+          <t>10.1007/s10800-011-0320-1</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/DDF.273-276.256</t>
+          <t>10.4028/www.scientific.net/DDF.283-286.38</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10.1016/j.jmmm.2020.167370</t>
+          <t>10.4028/www.scientific.net/DDF.273-276.256</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>10.1080/00084433.2017.1299907</t>
+          <t>10.1016/j.jmmm.2020.167370</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10.1016/j.msea.2006.12.019</t>
+          <t>10.1080/00084433.2017.1299907</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>10.1016/j.jmatprotec.2017.10.008</t>
+          <t>10.1016/j.msea.2006.12.019</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10.1016/j.scriptamat.2005.03.045</t>
+          <t>10.1016/j.jmatprotec.2017.10.008</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2019.01.022</t>
+          <t>10.1016/j.scriptamat.2005.03.045</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.591-593.141</t>
+          <t>10.1016/j.jnucmat.2019.01.022</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.416-418.23</t>
+          <t>10.4028/www.scientific.net/MSF.591-593.141</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.558-559.125</t>
+          <t>10.4028/www.scientific.net/MSF.416-418.23</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2006.04.019</t>
+          <t>10.4028/www.scientific.net/MSF.558-559.125</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10.1016/0263-4368(95)00049-6</t>
+          <t>10.1016/j.physc.2006.04.019</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2019.105080</t>
+          <t>10.1016/0263-4368(95)00049-6</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="inlineStr">
         <is>
+          <t>10.1016/j.ijrmhm.2019.105080</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>10.4028/www.scientific.net/MSF.408-412.517</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>10.1016/j.jmrt.2020.07.065</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.416-418.257</t>
+          <t>10.1016/j.jmrt.2020.07.065</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.1016/j.ijrmhm.2018.01.021</t>
+          <t>10.4028/www.scientific.net/MSF.416-418.257</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.498-499.146</t>
+          <t>10.1016/j.ijrmhm.2018.01.021</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>10.1007/s10853-014-8497-4</t>
+          <t>10.4028/www.scientific.net/MSF.498-499.146</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>10.1016/j.scriptamat.2009.10.002</t>
+          <t>10.1007/s10853-014-8497-4</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.467-470.519</t>
+          <t>10.1016/j.scriptamat.2009.10.002</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>10.4028/www.scientific.net/MSF.467-470.507</t>
+          <t>10.4028/www.scientific.net/MSF.467-470.519</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>10.1007/s11661-012-1408-x</t>
+          <t>10.4028/www.scientific.net/MSF.467-470.507</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2013.06.027</t>
+          <t>10.1007/s11661-012-1408-x</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>10.1007/s11669-017-0530-2</t>
+          <t>10.1016/j.actamat.2013.06.027</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.02.082</t>
+          <t>10.1007/s11669-017-0530-2</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10.1016/j.jnucmat.2008.11.029</t>
+          <t>10.1016/j.physc.2004.02.082</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10.3390/ma13183922</t>
+          <t>10.1016/j.jnucmat.2008.11.029</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>10.1016/j.actamat.2018.12.046</t>
+          <t>10.3390/ma13183922</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" t="inlineStr">
+        <is>
+          <t>10.1016/j.actamat.2018.12.046</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="inlineStr">
         <is>
           <t>10.1103/PhysRevLett.107.075503</t>
         </is>
